--- a/artfynd/A 31463-2022 artfynd.xlsx
+++ b/artfynd/A 31463-2022 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 31463-2022 artfynd.xlsx
+++ b/artfynd/A 31463-2022 artfynd.xlsx
@@ -2827,10 +2827,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>121146970</v>
+        <v>121146971</v>
       </c>
       <c r="B22" t="n">
-        <v>79583</v>
+        <v>78335</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2839,25 +2839,25 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6456</v>
+        <v>228912</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2867,10 +2867,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>532591</v>
+        <v>532980</v>
       </c>
       <c r="R22" t="n">
-        <v>6910435</v>
+        <v>6910252</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -3133,10 +3133,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>121146971</v>
+        <v>121146970</v>
       </c>
       <c r="B25" t="n">
-        <v>78335</v>
+        <v>79583</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3145,25 +3145,25 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>228912</v>
+        <v>6456</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3173,10 +3173,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>532980</v>
+        <v>532591</v>
       </c>
       <c r="R25" t="n">
-        <v>6910252</v>
+        <v>6910435</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>

--- a/artfynd/A 31463-2022 artfynd.xlsx
+++ b/artfynd/A 31463-2022 artfynd.xlsx
@@ -1699,10 +1699,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>121146969</v>
+        <v>121146982</v>
       </c>
       <c r="B11" t="n">
-        <v>95618</v>
+        <v>78337</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1715,21 +1715,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>53</v>
+        <v>6446</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1739,10 +1739,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>532986</v>
+        <v>532906</v>
       </c>
       <c r="R11" t="n">
-        <v>6910219</v>
+        <v>6910317</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1801,10 +1801,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>121146978</v>
+        <v>121146972</v>
       </c>
       <c r="B12" t="n">
-        <v>78334</v>
+        <v>80558</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1817,21 +1817,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6446</v>
+        <v>1049</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Kortskaftad ärgspik</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Microcalicium ahlneri</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1841,10 +1841,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>532668</v>
+        <v>532667</v>
       </c>
       <c r="R12" t="n">
-        <v>6910385</v>
+        <v>6910387</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1903,10 +1903,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>121146985</v>
+        <v>121146970</v>
       </c>
       <c r="B13" t="n">
-        <v>78598</v>
+        <v>79586</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1915,25 +1915,25 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6425</v>
+        <v>6456</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1943,10 +1943,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>532890</v>
+        <v>532591</v>
       </c>
       <c r="R13" t="n">
-        <v>6910366</v>
+        <v>6910435</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1981,18 +1981,12 @@
           <t>2024-11-04</t>
         </is>
       </c>
-      <c r="AC13" t="inlineStr">
-        <is>
-          <t>Garnlav På Tall</t>
-        </is>
-      </c>
       <c r="AD13" t="b">
         <v>0</v>
       </c>
       <c r="AE13" t="b">
         <v>0</v>
       </c>
-      <c r="AF13" t="inlineStr"/>
       <c r="AG13" t="b">
         <v>0</v>
       </c>
@@ -2011,10 +2005,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>121146984</v>
+        <v>121146980</v>
       </c>
       <c r="B14" t="n">
-        <v>90841</v>
+        <v>78337</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2023,25 +2017,25 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>1503</v>
+        <v>6446</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Gräddporing</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Sidera lenis</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(P.Karst.) Miettinen</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -2051,10 +2045,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>532952</v>
+        <v>532775</v>
       </c>
       <c r="R14" t="n">
-        <v>6910283</v>
+        <v>6910332</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2113,10 +2107,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>121146981</v>
+        <v>121146973</v>
       </c>
       <c r="B15" t="n">
-        <v>78334</v>
+        <v>78337</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2153,10 +2147,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>532844</v>
+        <v>532505</v>
       </c>
       <c r="R15" t="n">
-        <v>6910318</v>
+        <v>6910533</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2215,10 +2209,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>121146972</v>
+        <v>121146981</v>
       </c>
       <c r="B16" t="n">
-        <v>80555</v>
+        <v>78337</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2231,21 +2225,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>1049</v>
+        <v>6446</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Kortskaftad ärgspik</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Microcalicium ahlneri</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2255,10 +2249,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>532667</v>
+        <v>532844</v>
       </c>
       <c r="R16" t="n">
-        <v>6910387</v>
+        <v>6910318</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2317,10 +2311,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>121146977</v>
+        <v>121146985</v>
       </c>
       <c r="B17" t="n">
-        <v>78334</v>
+        <v>78601</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2333,21 +2327,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2357,10 +2351,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>532650</v>
+        <v>532890</v>
       </c>
       <c r="R17" t="n">
-        <v>6910410</v>
+        <v>6910366</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2395,12 +2389,18 @@
           <t>2024-11-04</t>
         </is>
       </c>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>Garnlav På Tall</t>
+        </is>
+      </c>
       <c r="AD17" t="b">
         <v>0</v>
       </c>
       <c r="AE17" t="b">
         <v>0</v>
       </c>
+      <c r="AF17" t="inlineStr"/>
       <c r="AG17" t="b">
         <v>0</v>
       </c>
@@ -2419,10 +2419,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>121146973</v>
+        <v>121146978</v>
       </c>
       <c r="B18" t="n">
-        <v>78334</v>
+        <v>78337</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2459,10 +2459,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>532505</v>
+        <v>532668</v>
       </c>
       <c r="R18" t="n">
-        <v>6910533</v>
+        <v>6910385</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2521,10 +2521,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>121146976</v>
+        <v>121146977</v>
       </c>
       <c r="B19" t="n">
-        <v>78334</v>
+        <v>78337</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2561,10 +2561,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>532590</v>
+        <v>532650</v>
       </c>
       <c r="R19" t="n">
-        <v>6910455</v>
+        <v>6910410</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2623,10 +2623,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>121146982</v>
+        <v>121146976</v>
       </c>
       <c r="B20" t="n">
-        <v>78334</v>
+        <v>78337</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2663,10 +2663,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>532906</v>
+        <v>532590</v>
       </c>
       <c r="R20" t="n">
-        <v>6910317</v>
+        <v>6910455</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2728,7 +2728,7 @@
         <v>121146979</v>
       </c>
       <c r="B21" t="n">
-        <v>78334</v>
+        <v>78337</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2827,10 +2827,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>121146971</v>
+        <v>121146969</v>
       </c>
       <c r="B22" t="n">
-        <v>78335</v>
+        <v>95628</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2843,21 +2843,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>228912</v>
+        <v>53</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2867,10 +2867,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>532980</v>
+        <v>532986</v>
       </c>
       <c r="R22" t="n">
-        <v>6910252</v>
+        <v>6910219</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2929,10 +2929,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>121146974</v>
+        <v>121146984</v>
       </c>
       <c r="B23" t="n">
-        <v>78334</v>
+        <v>90851</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -2941,25 +2941,25 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6446</v>
+        <v>1503</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Gräddporing</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Sidera lenis</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(P.Karst.) Miettinen</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2969,10 +2969,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>532543</v>
+        <v>532952</v>
       </c>
       <c r="R23" t="n">
-        <v>6910505</v>
+        <v>6910283</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3031,10 +3031,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>121146983</v>
+        <v>121146971</v>
       </c>
       <c r="B24" t="n">
-        <v>78334</v>
+        <v>78338</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3047,21 +3047,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6446</v>
+        <v>228912</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3071,7 +3071,7 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>532981</v>
+        <v>532980</v>
       </c>
       <c r="R24" t="n">
         <v>6910252</v>
@@ -3133,10 +3133,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>121146970</v>
+        <v>121146974</v>
       </c>
       <c r="B25" t="n">
-        <v>79583</v>
+        <v>78337</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3145,25 +3145,25 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6456</v>
+        <v>6446</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3173,10 +3173,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>532591</v>
+        <v>532543</v>
       </c>
       <c r="R25" t="n">
-        <v>6910435</v>
+        <v>6910505</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3235,10 +3235,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>121146980</v>
+        <v>121146983</v>
       </c>
       <c r="B26" t="n">
-        <v>78334</v>
+        <v>78337</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3275,10 +3275,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>532775</v>
+        <v>532981</v>
       </c>
       <c r="R26" t="n">
-        <v>6910332</v>
+        <v>6910252</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>

--- a/artfynd/A 31463-2022 artfynd.xlsx
+++ b/artfynd/A 31463-2022 artfynd.xlsx
@@ -1699,10 +1699,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>121146982</v>
+        <v>121146972</v>
       </c>
       <c r="B11" t="n">
-        <v>78337</v>
+        <v>80558</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1715,21 +1715,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6446</v>
+        <v>1049</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Kortskaftad ärgspik</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Microcalicium ahlneri</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1739,10 +1739,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>532906</v>
+        <v>532667</v>
       </c>
       <c r="R11" t="n">
-        <v>6910317</v>
+        <v>6910387</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1801,10 +1801,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>121146972</v>
+        <v>121146982</v>
       </c>
       <c r="B12" t="n">
-        <v>80558</v>
+        <v>78337</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1817,21 +1817,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>1049</v>
+        <v>6446</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Kortskaftad ärgspik</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Microcalicium ahlneri</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1841,10 +1841,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>532667</v>
+        <v>532906</v>
       </c>
       <c r="R12" t="n">
-        <v>6910387</v>
+        <v>6910317</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1903,10 +1903,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>121146970</v>
+        <v>121146980</v>
       </c>
       <c r="B13" t="n">
-        <v>79586</v>
+        <v>78337</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1915,25 +1915,25 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6456</v>
+        <v>6446</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1943,10 +1943,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>532591</v>
+        <v>532775</v>
       </c>
       <c r="R13" t="n">
-        <v>6910435</v>
+        <v>6910332</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2005,10 +2005,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>121146980</v>
+        <v>121146970</v>
       </c>
       <c r="B14" t="n">
-        <v>78337</v>
+        <v>79586</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2017,25 +2017,25 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6446</v>
+        <v>6456</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -2045,10 +2045,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>532775</v>
+        <v>532591</v>
       </c>
       <c r="R14" t="n">
-        <v>6910332</v>
+        <v>6910435</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>

--- a/artfynd/A 31463-2022 artfynd.xlsx
+++ b/artfynd/A 31463-2022 artfynd.xlsx
@@ -1699,10 +1699,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>121146972</v>
+        <v>121146982</v>
       </c>
       <c r="B11" t="n">
-        <v>80558</v>
+        <v>78337</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1715,21 +1715,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>1049</v>
+        <v>6446</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Kortskaftad ärgspik</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Microcalicium ahlneri</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1739,10 +1739,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>532667</v>
+        <v>532906</v>
       </c>
       <c r="R11" t="n">
-        <v>6910387</v>
+        <v>6910317</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1801,10 +1801,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>121146982</v>
+        <v>121146972</v>
       </c>
       <c r="B12" t="n">
-        <v>78337</v>
+        <v>80558</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1817,21 +1817,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6446</v>
+        <v>1049</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Kortskaftad ärgspik</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Microcalicium ahlneri</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1841,10 +1841,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>532906</v>
+        <v>532667</v>
       </c>
       <c r="R12" t="n">
-        <v>6910317</v>
+        <v>6910387</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>

--- a/artfynd/A 31463-2022 artfynd.xlsx
+++ b/artfynd/A 31463-2022 artfynd.xlsx
@@ -1699,10 +1699,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>121146982</v>
+        <v>121146970</v>
       </c>
       <c r="B11" t="n">
-        <v>78337</v>
+        <v>79586</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1711,25 +1711,25 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6446</v>
+        <v>6456</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1739,10 +1739,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>532906</v>
+        <v>532591</v>
       </c>
       <c r="R11" t="n">
-        <v>6910317</v>
+        <v>6910435</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1801,10 +1801,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>121146972</v>
+        <v>121146969</v>
       </c>
       <c r="B12" t="n">
-        <v>80558</v>
+        <v>95628</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1817,21 +1817,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>1049</v>
+        <v>53</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Kortskaftad ärgspik</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Microcalicium ahlneri</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1841,10 +1841,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>532667</v>
+        <v>532986</v>
       </c>
       <c r="R12" t="n">
-        <v>6910387</v>
+        <v>6910219</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1903,7 +1903,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>121146980</v>
+        <v>121146977</v>
       </c>
       <c r="B13" t="n">
         <v>78337</v>
@@ -1943,10 +1943,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>532775</v>
+        <v>532650</v>
       </c>
       <c r="R13" t="n">
-        <v>6910332</v>
+        <v>6910410</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2005,10 +2005,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>121146970</v>
+        <v>121146980</v>
       </c>
       <c r="B14" t="n">
-        <v>79586</v>
+        <v>78337</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2017,25 +2017,25 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6456</v>
+        <v>6446</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -2045,10 +2045,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>532591</v>
+        <v>532775</v>
       </c>
       <c r="R14" t="n">
-        <v>6910435</v>
+        <v>6910332</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2107,10 +2107,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>121146973</v>
+        <v>121146984</v>
       </c>
       <c r="B15" t="n">
-        <v>78337</v>
+        <v>90851</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2119,25 +2119,25 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6446</v>
+        <v>1503</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Gräddporing</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Sidera lenis</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(P.Karst.) Miettinen</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2147,10 +2147,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>532505</v>
+        <v>532952</v>
       </c>
       <c r="R15" t="n">
-        <v>6910533</v>
+        <v>6910283</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2209,10 +2209,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>121146981</v>
+        <v>121146985</v>
       </c>
       <c r="B16" t="n">
-        <v>78337</v>
+        <v>78601</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2225,21 +2225,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2249,10 +2249,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>532844</v>
+        <v>532890</v>
       </c>
       <c r="R16" t="n">
-        <v>6910318</v>
+        <v>6910366</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2287,12 +2287,18 @@
           <t>2024-11-04</t>
         </is>
       </c>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>Garnlav På Tall</t>
+        </is>
+      </c>
       <c r="AD16" t="b">
         <v>0</v>
       </c>
       <c r="AE16" t="b">
         <v>0</v>
       </c>
+      <c r="AF16" t="inlineStr"/>
       <c r="AG16" t="b">
         <v>0</v>
       </c>
@@ -2311,10 +2317,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>121146985</v>
+        <v>121146971</v>
       </c>
       <c r="B17" t="n">
-        <v>78601</v>
+        <v>78338</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2327,21 +2333,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2351,10 +2357,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>532890</v>
+        <v>532980</v>
       </c>
       <c r="R17" t="n">
-        <v>6910366</v>
+        <v>6910252</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2389,18 +2395,12 @@
           <t>2024-11-04</t>
         </is>
       </c>
-      <c r="AC17" t="inlineStr">
-        <is>
-          <t>Garnlav På Tall</t>
-        </is>
-      </c>
       <c r="AD17" t="b">
         <v>0</v>
       </c>
       <c r="AE17" t="b">
         <v>0</v>
       </c>
-      <c r="AF17" t="inlineStr"/>
       <c r="AG17" t="b">
         <v>0</v>
       </c>
@@ -2419,10 +2419,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>121146978</v>
+        <v>121146972</v>
       </c>
       <c r="B18" t="n">
-        <v>78337</v>
+        <v>80558</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2435,21 +2435,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6446</v>
+        <v>1049</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Kortskaftad ärgspik</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Microcalicium ahlneri</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2459,10 +2459,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>532668</v>
+        <v>532667</v>
       </c>
       <c r="R18" t="n">
-        <v>6910385</v>
+        <v>6910387</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2521,7 +2521,7 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>121146977</v>
+        <v>121146982</v>
       </c>
       <c r="B19" t="n">
         <v>78337</v>
@@ -2561,10 +2561,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>532650</v>
+        <v>532906</v>
       </c>
       <c r="R19" t="n">
-        <v>6910410</v>
+        <v>6910317</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2623,7 +2623,7 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>121146976</v>
+        <v>121146983</v>
       </c>
       <c r="B20" t="n">
         <v>78337</v>
@@ -2663,10 +2663,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>532590</v>
+        <v>532981</v>
       </c>
       <c r="R20" t="n">
-        <v>6910455</v>
+        <v>6910252</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2725,7 +2725,7 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>121146979</v>
+        <v>121146973</v>
       </c>
       <c r="B21" t="n">
         <v>78337</v>
@@ -2765,10 +2765,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>532733</v>
+        <v>532505</v>
       </c>
       <c r="R21" t="n">
-        <v>6910348</v>
+        <v>6910533</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2827,10 +2827,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>121146969</v>
+        <v>121146976</v>
       </c>
       <c r="B22" t="n">
-        <v>95628</v>
+        <v>78337</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2843,21 +2843,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>53</v>
+        <v>6446</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2867,10 +2867,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>532986</v>
+        <v>532590</v>
       </c>
       <c r="R22" t="n">
-        <v>6910219</v>
+        <v>6910455</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2929,10 +2929,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>121146984</v>
+        <v>121146978</v>
       </c>
       <c r="B23" t="n">
-        <v>90851</v>
+        <v>78337</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -2941,25 +2941,25 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>1503</v>
+        <v>6446</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Gräddporing</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Sidera lenis</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(P.Karst.) Miettinen</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2969,10 +2969,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>532952</v>
+        <v>532668</v>
       </c>
       <c r="R23" t="n">
-        <v>6910283</v>
+        <v>6910385</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3031,10 +3031,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>121146971</v>
+        <v>121146981</v>
       </c>
       <c r="B24" t="n">
-        <v>78338</v>
+        <v>78337</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3047,21 +3047,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>228912</v>
+        <v>6446</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3071,10 +3071,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>532980</v>
+        <v>532844</v>
       </c>
       <c r="R24" t="n">
-        <v>6910252</v>
+        <v>6910318</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3235,7 +3235,7 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>121146983</v>
+        <v>121146979</v>
       </c>
       <c r="B26" t="n">
         <v>78337</v>
@@ -3275,10 +3275,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>532981</v>
+        <v>532733</v>
       </c>
       <c r="R26" t="n">
-        <v>6910252</v>
+        <v>6910348</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>

--- a/artfynd/A 31463-2022 artfynd.xlsx
+++ b/artfynd/A 31463-2022 artfynd.xlsx
@@ -1699,10 +1699,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>121146970</v>
+        <v>121146971</v>
       </c>
       <c r="B11" t="n">
-        <v>79586</v>
+        <v>78341</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1711,25 +1711,25 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6456</v>
+        <v>228912</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1739,10 +1739,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>532591</v>
+        <v>532980</v>
       </c>
       <c r="R11" t="n">
-        <v>6910435</v>
+        <v>6910252</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1801,10 +1801,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>121146969</v>
+        <v>121146978</v>
       </c>
       <c r="B12" t="n">
-        <v>95628</v>
+        <v>78340</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1817,21 +1817,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>53</v>
+        <v>6446</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1841,10 +1841,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>532986</v>
+        <v>532668</v>
       </c>
       <c r="R12" t="n">
-        <v>6910219</v>
+        <v>6910385</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1903,10 +1903,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>121146977</v>
+        <v>121146980</v>
       </c>
       <c r="B13" t="n">
-        <v>78337</v>
+        <v>78340</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1943,10 +1943,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>532650</v>
+        <v>532775</v>
       </c>
       <c r="R13" t="n">
-        <v>6910410</v>
+        <v>6910332</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2005,10 +2005,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>121146980</v>
+        <v>121146969</v>
       </c>
       <c r="B14" t="n">
-        <v>78337</v>
+        <v>95641</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2021,21 +2021,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6446</v>
+        <v>53</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -2045,10 +2045,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>532775</v>
+        <v>532986</v>
       </c>
       <c r="R14" t="n">
-        <v>6910332</v>
+        <v>6910219</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2110,7 +2110,7 @@
         <v>121146984</v>
       </c>
       <c r="B15" t="n">
-        <v>90851</v>
+        <v>90863</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2209,10 +2209,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>121146985</v>
+        <v>121146981</v>
       </c>
       <c r="B16" t="n">
-        <v>78601</v>
+        <v>78340</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2225,21 +2225,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2249,10 +2249,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>532890</v>
+        <v>532844</v>
       </c>
       <c r="R16" t="n">
-        <v>6910366</v>
+        <v>6910318</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2287,18 +2287,12 @@
           <t>2024-11-04</t>
         </is>
       </c>
-      <c r="AC16" t="inlineStr">
-        <is>
-          <t>Garnlav På Tall</t>
-        </is>
-      </c>
       <c r="AD16" t="b">
         <v>0</v>
       </c>
       <c r="AE16" t="b">
         <v>0</v>
       </c>
-      <c r="AF16" t="inlineStr"/>
       <c r="AG16" t="b">
         <v>0</v>
       </c>
@@ -2317,10 +2311,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>121146971</v>
+        <v>121146972</v>
       </c>
       <c r="B17" t="n">
-        <v>78338</v>
+        <v>80561</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2333,21 +2327,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>228912</v>
+        <v>1049</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Kortskaftad ärgspik</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Microcalicium ahlneri</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2357,10 +2351,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>532980</v>
+        <v>532667</v>
       </c>
       <c r="R17" t="n">
-        <v>6910252</v>
+        <v>6910387</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2419,10 +2413,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>121146972</v>
+        <v>121146985</v>
       </c>
       <c r="B18" t="n">
-        <v>80558</v>
+        <v>78604</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2435,21 +2429,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>1049</v>
+        <v>6425</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Kortskaftad ärgspik</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Microcalicium ahlneri</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2459,10 +2453,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>532667</v>
+        <v>532890</v>
       </c>
       <c r="R18" t="n">
-        <v>6910387</v>
+        <v>6910366</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2497,12 +2491,18 @@
           <t>2024-11-04</t>
         </is>
       </c>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>Garnlav På Tall</t>
+        </is>
+      </c>
       <c r="AD18" t="b">
         <v>0</v>
       </c>
       <c r="AE18" t="b">
         <v>0</v>
       </c>
+      <c r="AF18" t="inlineStr"/>
       <c r="AG18" t="b">
         <v>0</v>
       </c>
@@ -2521,10 +2521,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>121146982</v>
+        <v>121146973</v>
       </c>
       <c r="B19" t="n">
-        <v>78337</v>
+        <v>78340</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2561,10 +2561,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>532906</v>
+        <v>532505</v>
       </c>
       <c r="R19" t="n">
-        <v>6910317</v>
+        <v>6910533</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2623,10 +2623,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>121146983</v>
+        <v>121146970</v>
       </c>
       <c r="B20" t="n">
-        <v>78337</v>
+        <v>79589</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2635,25 +2635,25 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6446</v>
+        <v>6456</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2663,10 +2663,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>532981</v>
+        <v>532591</v>
       </c>
       <c r="R20" t="n">
-        <v>6910252</v>
+        <v>6910435</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2725,10 +2725,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>121146973</v>
+        <v>121146976</v>
       </c>
       <c r="B21" t="n">
-        <v>78337</v>
+        <v>78340</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2765,10 +2765,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>532505</v>
+        <v>532590</v>
       </c>
       <c r="R21" t="n">
-        <v>6910533</v>
+        <v>6910455</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2827,10 +2827,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>121146976</v>
+        <v>121146977</v>
       </c>
       <c r="B22" t="n">
-        <v>78337</v>
+        <v>78340</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2867,10 +2867,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>532590</v>
+        <v>532650</v>
       </c>
       <c r="R22" t="n">
-        <v>6910455</v>
+        <v>6910410</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2929,10 +2929,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>121146978</v>
+        <v>121146974</v>
       </c>
       <c r="B23" t="n">
-        <v>78337</v>
+        <v>78340</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -2969,10 +2969,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>532668</v>
+        <v>532543</v>
       </c>
       <c r="R23" t="n">
-        <v>6910385</v>
+        <v>6910505</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3031,10 +3031,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>121146981</v>
+        <v>121146983</v>
       </c>
       <c r="B24" t="n">
-        <v>78337</v>
+        <v>78340</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3071,10 +3071,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>532844</v>
+        <v>532981</v>
       </c>
       <c r="R24" t="n">
-        <v>6910318</v>
+        <v>6910252</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3133,10 +3133,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>121146974</v>
+        <v>121146979</v>
       </c>
       <c r="B25" t="n">
-        <v>78337</v>
+        <v>78340</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3173,10 +3173,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>532543</v>
+        <v>532733</v>
       </c>
       <c r="R25" t="n">
-        <v>6910505</v>
+        <v>6910348</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3235,10 +3235,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>121146979</v>
+        <v>121146982</v>
       </c>
       <c r="B26" t="n">
-        <v>78337</v>
+        <v>78340</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3275,10 +3275,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>532733</v>
+        <v>532906</v>
       </c>
       <c r="R26" t="n">
-        <v>6910348</v>
+        <v>6910317</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>

--- a/artfynd/A 31463-2022 artfynd.xlsx
+++ b/artfynd/A 31463-2022 artfynd.xlsx
@@ -1699,10 +1699,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>121146971</v>
+        <v>121146976</v>
       </c>
       <c r="B11" t="n">
-        <v>78341</v>
+        <v>78340</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1715,21 +1715,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>228912</v>
+        <v>6446</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1739,10 +1739,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>532980</v>
+        <v>532590</v>
       </c>
       <c r="R11" t="n">
-        <v>6910252</v>
+        <v>6910455</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1801,7 +1801,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>121146978</v>
+        <v>121146983</v>
       </c>
       <c r="B12" t="n">
         <v>78340</v>
@@ -1841,10 +1841,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>532668</v>
+        <v>532981</v>
       </c>
       <c r="R12" t="n">
-        <v>6910385</v>
+        <v>6910252</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1903,10 +1903,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>121146980</v>
+        <v>121146971</v>
       </c>
       <c r="B13" t="n">
-        <v>78340</v>
+        <v>78341</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1919,21 +1919,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6446</v>
+        <v>228912</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1943,10 +1943,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>532775</v>
+        <v>532980</v>
       </c>
       <c r="R13" t="n">
-        <v>6910332</v>
+        <v>6910252</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2005,10 +2005,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>121146969</v>
+        <v>121146972</v>
       </c>
       <c r="B14" t="n">
-        <v>95641</v>
+        <v>80561</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2021,21 +2021,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>53</v>
+        <v>1049</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Kortskaftad ärgspik</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Microcalicium ahlneri</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -2045,10 +2045,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>532986</v>
+        <v>532667</v>
       </c>
       <c r="R14" t="n">
-        <v>6910219</v>
+        <v>6910387</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2107,10 +2107,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>121146984</v>
+        <v>121146985</v>
       </c>
       <c r="B15" t="n">
-        <v>90863</v>
+        <v>78604</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2119,25 +2119,25 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>1503</v>
+        <v>6425</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Gräddporing</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Sidera lenis</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(P.Karst.) Miettinen</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2147,10 +2147,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>532952</v>
+        <v>532890</v>
       </c>
       <c r="R15" t="n">
-        <v>6910283</v>
+        <v>6910366</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2185,12 +2185,18 @@
           <t>2024-11-04</t>
         </is>
       </c>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>Garnlav På Tall</t>
+        </is>
+      </c>
       <c r="AD15" t="b">
         <v>0</v>
       </c>
       <c r="AE15" t="b">
         <v>0</v>
       </c>
+      <c r="AF15" t="inlineStr"/>
       <c r="AG15" t="b">
         <v>0</v>
       </c>
@@ -2209,7 +2215,7 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>121146981</v>
+        <v>121146980</v>
       </c>
       <c r="B16" t="n">
         <v>78340</v>
@@ -2249,10 +2255,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>532844</v>
+        <v>532775</v>
       </c>
       <c r="R16" t="n">
-        <v>6910318</v>
+        <v>6910332</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2311,10 +2317,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>121146972</v>
+        <v>121146974</v>
       </c>
       <c r="B17" t="n">
-        <v>80561</v>
+        <v>78340</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2327,21 +2333,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>1049</v>
+        <v>6446</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Kortskaftad ärgspik</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Microcalicium ahlneri</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2351,10 +2357,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>532667</v>
+        <v>532543</v>
       </c>
       <c r="R17" t="n">
-        <v>6910387</v>
+        <v>6910505</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2413,10 +2419,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>121146985</v>
+        <v>121146977</v>
       </c>
       <c r="B18" t="n">
-        <v>78604</v>
+        <v>78340</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2429,21 +2435,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2453,10 +2459,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>532890</v>
+        <v>532650</v>
       </c>
       <c r="R18" t="n">
-        <v>6910366</v>
+        <v>6910410</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2491,18 +2497,12 @@
           <t>2024-11-04</t>
         </is>
       </c>
-      <c r="AC18" t="inlineStr">
-        <is>
-          <t>Garnlav På Tall</t>
-        </is>
-      </c>
       <c r="AD18" t="b">
         <v>0</v>
       </c>
       <c r="AE18" t="b">
         <v>0</v>
       </c>
-      <c r="AF18" t="inlineStr"/>
       <c r="AG18" t="b">
         <v>0</v>
       </c>
@@ -2521,10 +2521,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>121146973</v>
+        <v>121146969</v>
       </c>
       <c r="B19" t="n">
-        <v>78340</v>
+        <v>95642</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2537,21 +2537,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6446</v>
+        <v>53</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2561,10 +2561,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>532505</v>
+        <v>532986</v>
       </c>
       <c r="R19" t="n">
-        <v>6910533</v>
+        <v>6910219</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2623,10 +2623,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>121146970</v>
+        <v>121146973</v>
       </c>
       <c r="B20" t="n">
-        <v>79589</v>
+        <v>78340</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2635,25 +2635,25 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6456</v>
+        <v>6446</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2663,10 +2663,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>532591</v>
+        <v>532505</v>
       </c>
       <c r="R20" t="n">
-        <v>6910435</v>
+        <v>6910533</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2725,7 +2725,7 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>121146976</v>
+        <v>121146981</v>
       </c>
       <c r="B21" t="n">
         <v>78340</v>
@@ -2765,10 +2765,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>532590</v>
+        <v>532844</v>
       </c>
       <c r="R21" t="n">
-        <v>6910455</v>
+        <v>6910318</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2827,7 +2827,7 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>121146977</v>
+        <v>121146979</v>
       </c>
       <c r="B22" t="n">
         <v>78340</v>
@@ -2867,10 +2867,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>532650</v>
+        <v>532733</v>
       </c>
       <c r="R22" t="n">
-        <v>6910410</v>
+        <v>6910348</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2929,10 +2929,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>121146974</v>
+        <v>121146984</v>
       </c>
       <c r="B23" t="n">
-        <v>78340</v>
+        <v>90864</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -2941,25 +2941,25 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6446</v>
+        <v>1503</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Gräddporing</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Sidera lenis</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(P.Karst.) Miettinen</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2969,10 +2969,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>532543</v>
+        <v>532952</v>
       </c>
       <c r="R23" t="n">
-        <v>6910505</v>
+        <v>6910283</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3031,7 +3031,7 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>121146983</v>
+        <v>121146978</v>
       </c>
       <c r="B24" t="n">
         <v>78340</v>
@@ -3071,10 +3071,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>532981</v>
+        <v>532668</v>
       </c>
       <c r="R24" t="n">
-        <v>6910252</v>
+        <v>6910385</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3133,10 +3133,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>121146979</v>
+        <v>121146970</v>
       </c>
       <c r="B25" t="n">
-        <v>78340</v>
+        <v>79589</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3145,25 +3145,25 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6446</v>
+        <v>6456</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3173,10 +3173,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>532733</v>
+        <v>532591</v>
       </c>
       <c r="R25" t="n">
-        <v>6910348</v>
+        <v>6910435</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>

--- a/artfynd/A 31463-2022 artfynd.xlsx
+++ b/artfynd/A 31463-2022 artfynd.xlsx
@@ -1699,10 +1699,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>121146976</v>
+        <v>121146980</v>
       </c>
       <c r="B11" t="n">
-        <v>78340</v>
+        <v>78343</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1739,10 +1739,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>532590</v>
+        <v>532775</v>
       </c>
       <c r="R11" t="n">
-        <v>6910455</v>
+        <v>6910332</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1801,10 +1801,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>121146983</v>
+        <v>121146979</v>
       </c>
       <c r="B12" t="n">
-        <v>78340</v>
+        <v>78343</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1841,10 +1841,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>532981</v>
+        <v>532733</v>
       </c>
       <c r="R12" t="n">
-        <v>6910252</v>
+        <v>6910348</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1903,10 +1903,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>121146971</v>
+        <v>121146970</v>
       </c>
       <c r="B13" t="n">
-        <v>78341</v>
+        <v>79592</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1915,25 +1915,25 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>228912</v>
+        <v>6456</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1943,10 +1943,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>532980</v>
+        <v>532591</v>
       </c>
       <c r="R13" t="n">
-        <v>6910252</v>
+        <v>6910435</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2005,10 +2005,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>121146972</v>
+        <v>121146985</v>
       </c>
       <c r="B14" t="n">
-        <v>80561</v>
+        <v>78607</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2021,21 +2021,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>1049</v>
+        <v>6425</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Kortskaftad ärgspik</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Microcalicium ahlneri</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -2045,10 +2045,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>532667</v>
+        <v>532890</v>
       </c>
       <c r="R14" t="n">
-        <v>6910387</v>
+        <v>6910366</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2083,12 +2083,18 @@
           <t>2024-11-04</t>
         </is>
       </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>Garnlav På Tall</t>
+        </is>
+      </c>
       <c r="AD14" t="b">
         <v>0</v>
       </c>
       <c r="AE14" t="b">
         <v>0</v>
       </c>
+      <c r="AF14" t="inlineStr"/>
       <c r="AG14" t="b">
         <v>0</v>
       </c>
@@ -2107,10 +2113,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>121146985</v>
+        <v>121146976</v>
       </c>
       <c r="B15" t="n">
-        <v>78604</v>
+        <v>78343</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2123,21 +2129,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2147,10 +2153,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>532890</v>
+        <v>532590</v>
       </c>
       <c r="R15" t="n">
-        <v>6910366</v>
+        <v>6910455</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2185,18 +2191,12 @@
           <t>2024-11-04</t>
         </is>
       </c>
-      <c r="AC15" t="inlineStr">
-        <is>
-          <t>Garnlav På Tall</t>
-        </is>
-      </c>
       <c r="AD15" t="b">
         <v>0</v>
       </c>
       <c r="AE15" t="b">
         <v>0</v>
       </c>
-      <c r="AF15" t="inlineStr"/>
       <c r="AG15" t="b">
         <v>0</v>
       </c>
@@ -2215,10 +2215,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>121146980</v>
+        <v>121146969</v>
       </c>
       <c r="B16" t="n">
-        <v>78340</v>
+        <v>95645</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2231,21 +2231,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6446</v>
+        <v>53</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2255,10 +2255,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>532775</v>
+        <v>532986</v>
       </c>
       <c r="R16" t="n">
-        <v>6910332</v>
+        <v>6910219</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2317,10 +2317,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>121146974</v>
+        <v>121146977</v>
       </c>
       <c r="B17" t="n">
-        <v>78340</v>
+        <v>78343</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2357,10 +2357,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>532543</v>
+        <v>532650</v>
       </c>
       <c r="R17" t="n">
-        <v>6910505</v>
+        <v>6910410</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2419,10 +2419,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>121146977</v>
+        <v>121146974</v>
       </c>
       <c r="B18" t="n">
-        <v>78340</v>
+        <v>78343</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2459,10 +2459,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>532650</v>
+        <v>532543</v>
       </c>
       <c r="R18" t="n">
-        <v>6910410</v>
+        <v>6910505</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2521,10 +2521,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>121146969</v>
+        <v>121146982</v>
       </c>
       <c r="B19" t="n">
-        <v>95642</v>
+        <v>78343</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2537,21 +2537,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>53</v>
+        <v>6446</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2561,10 +2561,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>532986</v>
+        <v>532906</v>
       </c>
       <c r="R19" t="n">
-        <v>6910219</v>
+        <v>6910317</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2623,10 +2623,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>121146973</v>
+        <v>121146972</v>
       </c>
       <c r="B20" t="n">
-        <v>78340</v>
+        <v>80564</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2639,21 +2639,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6446</v>
+        <v>1049</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Kortskaftad ärgspik</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Microcalicium ahlneri</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2663,10 +2663,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>532505</v>
+        <v>532667</v>
       </c>
       <c r="R20" t="n">
-        <v>6910533</v>
+        <v>6910387</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2725,10 +2725,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>121146981</v>
+        <v>121146978</v>
       </c>
       <c r="B21" t="n">
-        <v>78340</v>
+        <v>78343</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2765,10 +2765,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>532844</v>
+        <v>532668</v>
       </c>
       <c r="R21" t="n">
-        <v>6910318</v>
+        <v>6910385</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2827,10 +2827,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>121146979</v>
+        <v>121146973</v>
       </c>
       <c r="B22" t="n">
-        <v>78340</v>
+        <v>78343</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2867,10 +2867,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>532733</v>
+        <v>532505</v>
       </c>
       <c r="R22" t="n">
-        <v>6910348</v>
+        <v>6910533</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2929,10 +2929,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>121146984</v>
+        <v>121146981</v>
       </c>
       <c r="B23" t="n">
-        <v>90864</v>
+        <v>78343</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -2941,25 +2941,25 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>1503</v>
+        <v>6446</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Gräddporing</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Sidera lenis</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(P.Karst.) Miettinen</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2969,10 +2969,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>532952</v>
+        <v>532844</v>
       </c>
       <c r="R23" t="n">
-        <v>6910283</v>
+        <v>6910318</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3031,10 +3031,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>121146978</v>
+        <v>121146971</v>
       </c>
       <c r="B24" t="n">
-        <v>78340</v>
+        <v>78344</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3047,21 +3047,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6446</v>
+        <v>228912</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3071,10 +3071,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>532668</v>
+        <v>532980</v>
       </c>
       <c r="R24" t="n">
-        <v>6910385</v>
+        <v>6910252</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3133,10 +3133,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>121146970</v>
+        <v>121146984</v>
       </c>
       <c r="B25" t="n">
-        <v>79589</v>
+        <v>90867</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3145,25 +3145,25 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6456</v>
+        <v>1503</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Gräddporing</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Sidera lenis</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(P.Karst.) Miettinen</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3173,10 +3173,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>532591</v>
+        <v>532952</v>
       </c>
       <c r="R25" t="n">
-        <v>6910435</v>
+        <v>6910283</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3235,10 +3235,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>121146982</v>
+        <v>121146983</v>
       </c>
       <c r="B26" t="n">
-        <v>78340</v>
+        <v>78343</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3275,10 +3275,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>532906</v>
+        <v>532981</v>
       </c>
       <c r="R26" t="n">
-        <v>6910317</v>
+        <v>6910252</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>

--- a/artfynd/A 31463-2022 artfynd.xlsx
+++ b/artfynd/A 31463-2022 artfynd.xlsx
@@ -1699,10 +1699,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>121146980</v>
+        <v>121146969</v>
       </c>
       <c r="B11" t="n">
-        <v>78343</v>
+        <v>95645</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1715,21 +1715,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6446</v>
+        <v>53</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1739,10 +1739,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>532775</v>
+        <v>532986</v>
       </c>
       <c r="R11" t="n">
-        <v>6910332</v>
+        <v>6910219</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1801,7 +1801,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>121146979</v>
+        <v>121146983</v>
       </c>
       <c r="B12" t="n">
         <v>78343</v>
@@ -1841,10 +1841,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>532733</v>
+        <v>532981</v>
       </c>
       <c r="R12" t="n">
-        <v>6910348</v>
+        <v>6910252</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1903,10 +1903,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>121146970</v>
+        <v>121146976</v>
       </c>
       <c r="B13" t="n">
-        <v>79592</v>
+        <v>78343</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1915,25 +1915,25 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6456</v>
+        <v>6446</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1943,10 +1943,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>532591</v>
+        <v>532590</v>
       </c>
       <c r="R13" t="n">
-        <v>6910435</v>
+        <v>6910455</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2005,10 +2005,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>121146985</v>
+        <v>121146980</v>
       </c>
       <c r="B14" t="n">
-        <v>78607</v>
+        <v>78343</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2021,21 +2021,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -2045,10 +2045,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>532890</v>
+        <v>532775</v>
       </c>
       <c r="R14" t="n">
-        <v>6910366</v>
+        <v>6910332</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2083,18 +2083,12 @@
           <t>2024-11-04</t>
         </is>
       </c>
-      <c r="AC14" t="inlineStr">
-        <is>
-          <t>Garnlav På Tall</t>
-        </is>
-      </c>
       <c r="AD14" t="b">
         <v>0</v>
       </c>
       <c r="AE14" t="b">
         <v>0</v>
       </c>
-      <c r="AF14" t="inlineStr"/>
       <c r="AG14" t="b">
         <v>0</v>
       </c>
@@ -2113,7 +2107,7 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>121146976</v>
+        <v>121146979</v>
       </c>
       <c r="B15" t="n">
         <v>78343</v>
@@ -2153,10 +2147,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>532590</v>
+        <v>532733</v>
       </c>
       <c r="R15" t="n">
-        <v>6910455</v>
+        <v>6910348</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2215,10 +2209,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>121146969</v>
+        <v>121146972</v>
       </c>
       <c r="B16" t="n">
-        <v>95645</v>
+        <v>80564</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2231,21 +2225,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>53</v>
+        <v>1049</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Kortskaftad ärgspik</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Microcalicium ahlneri</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2255,10 +2249,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>532986</v>
+        <v>532667</v>
       </c>
       <c r="R16" t="n">
-        <v>6910219</v>
+        <v>6910387</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2317,7 +2311,7 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>121146977</v>
+        <v>121146973</v>
       </c>
       <c r="B17" t="n">
         <v>78343</v>
@@ -2357,10 +2351,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>532650</v>
+        <v>532505</v>
       </c>
       <c r="R17" t="n">
-        <v>6910410</v>
+        <v>6910533</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2419,10 +2413,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>121146974</v>
+        <v>121146984</v>
       </c>
       <c r="B18" t="n">
-        <v>78343</v>
+        <v>90867</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2431,25 +2425,25 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6446</v>
+        <v>1503</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Gräddporing</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Sidera lenis</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(P.Karst.) Miettinen</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2459,10 +2453,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>532543</v>
+        <v>532952</v>
       </c>
       <c r="R18" t="n">
-        <v>6910505</v>
+        <v>6910283</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2521,10 +2515,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>121146982</v>
+        <v>121146970</v>
       </c>
       <c r="B19" t="n">
-        <v>78343</v>
+        <v>79592</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2533,25 +2527,25 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6446</v>
+        <v>6456</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2561,10 +2555,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>532906</v>
+        <v>532591</v>
       </c>
       <c r="R19" t="n">
-        <v>6910317</v>
+        <v>6910435</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2623,10 +2617,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>121146972</v>
+        <v>121146985</v>
       </c>
       <c r="B20" t="n">
-        <v>80564</v>
+        <v>78607</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2639,21 +2633,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>1049</v>
+        <v>6425</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Kortskaftad ärgspik</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Microcalicium ahlneri</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2663,10 +2657,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>532667</v>
+        <v>532890</v>
       </c>
       <c r="R20" t="n">
-        <v>6910387</v>
+        <v>6910366</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2701,12 +2695,18 @@
           <t>2024-11-04</t>
         </is>
       </c>
+      <c r="AC20" t="inlineStr">
+        <is>
+          <t>Garnlav På Tall</t>
+        </is>
+      </c>
       <c r="AD20" t="b">
         <v>0</v>
       </c>
       <c r="AE20" t="b">
         <v>0</v>
       </c>
+      <c r="AF20" t="inlineStr"/>
       <c r="AG20" t="b">
         <v>0</v>
       </c>
@@ -2725,7 +2725,7 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>121146978</v>
+        <v>121146982</v>
       </c>
       <c r="B21" t="n">
         <v>78343</v>
@@ -2765,10 +2765,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>532668</v>
+        <v>532906</v>
       </c>
       <c r="R21" t="n">
-        <v>6910385</v>
+        <v>6910317</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2827,7 +2827,7 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>121146973</v>
+        <v>121146981</v>
       </c>
       <c r="B22" t="n">
         <v>78343</v>
@@ -2867,10 +2867,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>532505</v>
+        <v>532844</v>
       </c>
       <c r="R22" t="n">
-        <v>6910533</v>
+        <v>6910318</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2929,7 +2929,7 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>121146981</v>
+        <v>121146977</v>
       </c>
       <c r="B23" t="n">
         <v>78343</v>
@@ -2969,10 +2969,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>532844</v>
+        <v>532650</v>
       </c>
       <c r="R23" t="n">
-        <v>6910318</v>
+        <v>6910410</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3133,10 +3133,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>121146984</v>
+        <v>121146978</v>
       </c>
       <c r="B25" t="n">
-        <v>90867</v>
+        <v>78343</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3145,25 +3145,25 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>1503</v>
+        <v>6446</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Gräddporing</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Sidera lenis</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(P.Karst.) Miettinen</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3173,10 +3173,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>532952</v>
+        <v>532668</v>
       </c>
       <c r="R25" t="n">
-        <v>6910283</v>
+        <v>6910385</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3235,7 +3235,7 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>121146983</v>
+        <v>121146974</v>
       </c>
       <c r="B26" t="n">
         <v>78343</v>
@@ -3275,10 +3275,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>532981</v>
+        <v>532543</v>
       </c>
       <c r="R26" t="n">
-        <v>6910252</v>
+        <v>6910505</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>

--- a/artfynd/A 31463-2022 artfynd.xlsx
+++ b/artfynd/A 31463-2022 artfynd.xlsx
@@ -1699,10 +1699,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>121146969</v>
+        <v>121146983</v>
       </c>
       <c r="B11" t="n">
-        <v>95645</v>
+        <v>78343</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1715,21 +1715,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>53</v>
+        <v>6446</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1739,10 +1739,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>532986</v>
+        <v>532981</v>
       </c>
       <c r="R11" t="n">
-        <v>6910219</v>
+        <v>6910252</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1801,10 +1801,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>121146983</v>
+        <v>121146969</v>
       </c>
       <c r="B12" t="n">
-        <v>78343</v>
+        <v>95645</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1817,21 +1817,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6446</v>
+        <v>53</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1841,10 +1841,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>532981</v>
+        <v>532986</v>
       </c>
       <c r="R12" t="n">
-        <v>6910252</v>
+        <v>6910219</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>

--- a/artfynd/A 31463-2022 artfynd.xlsx
+++ b/artfynd/A 31463-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY26"/>
+  <dimension ref="A1:AY30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,53 +675,48 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>67288989</v>
+        <v>121146969</v>
       </c>
       <c r="B2" t="n">
-        <v>96334</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>97358</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>220787</v>
+        <v>53</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Barrskog Ö Nymyrdalen, Hls</t>
+          <t>Nymyran, Hls</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>532454.8555116563</v>
+        <v>532986</v>
       </c>
       <c r="R2" t="n">
-        <v>6910565.224504324</v>
+        <v>6910219</v>
       </c>
       <c r="S2" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -745,22 +740,12 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2017-08-25</t>
-        </is>
-      </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2024-11-04</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2017-08-25</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2024-11-04</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -775,65 +760,60 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Jan Henriksson</t>
+          <t>Annica Berglind</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Jan Henriksson</t>
+          <t>Annica Berglind</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>67288990</v>
+        <v>121146972</v>
       </c>
       <c r="B3" t="n">
-        <v>96334</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>81312</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>220787</v>
+        <v>1049</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Kortskaftad ärgspik</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Microcalicium ahlneri</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Barrskog Ö Nymyrdalen, Hls</t>
+          <t>Nymyran, Hls</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>532503.8262744579</v>
+        <v>532667</v>
       </c>
       <c r="R3" t="n">
-        <v>6910603.815837521</v>
+        <v>6910387</v>
       </c>
       <c r="S3" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -857,22 +837,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2017-08-25</t>
-        </is>
-      </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2024-11-04</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2017-08-25</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2024-11-04</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -887,65 +857,60 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Jan Henriksson</t>
+          <t>Annica Berglind</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Jan Henriksson</t>
+          <t>Annica Berglind</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>67288988</v>
+        <v>121146984</v>
       </c>
       <c r="B4" t="n">
-        <v>77506</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92083</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6425</v>
+        <v>1503</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gräddporing</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Sidera lenis</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Miettinen</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Barrskog Ö Nymyrdalen, Hls</t>
+          <t>Nymyran, Hls</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>532445.9260191878</v>
+        <v>532952</v>
       </c>
       <c r="R4" t="n">
-        <v>6910573.970062403</v>
+        <v>6910283</v>
       </c>
       <c r="S4" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -969,22 +934,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2017-08-25</t>
-        </is>
-      </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2024-11-04</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2017-08-25</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2024-11-04</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -999,27 +954,22 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Jan Henriksson</t>
+          <t>Annica Berglind</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Jan Henriksson</t>
+          <t>Annica Berglind</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>67288992</v>
+        <v>89119066</v>
       </c>
       <c r="B5" t="n">
-        <v>77258</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>97453</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1027,36 +977,34 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6446</v>
+        <v>1841</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Vedflikmossa</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Lophozia guttulata</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Lindb. &amp; Arnell) A.Evans</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
-      <c r="J5" t="inlineStr"/>
-      <c r="K5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Barrskog Ö Nymyran, Hls</t>
+          <t>VSV Nymyran, Hls</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>532474.9609741571</v>
+        <v>533001</v>
       </c>
       <c r="R5" t="n">
-        <v>6910556.122348499</v>
+        <v>6910249</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1083,22 +1031,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2017-08-25</t>
-        </is>
-      </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2020-07-26</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2017-08-25</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2020-07-26</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1125,19 +1063,14 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>89119052</v>
+        <v>67288988</v>
       </c>
       <c r="B6" t="n">
-        <v>77506</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E6" t="n">
@@ -1161,14 +1094,14 @@
       <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>VSV Nymyran, Hls</t>
+          <t>Barrskog Ö Nymyrdalen, Hls</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>532896.0418381225</v>
+        <v>532446</v>
       </c>
       <c r="R6" t="n">
-        <v>6910340.814144458</v>
+        <v>6910574</v>
       </c>
       <c r="S6" t="n">
         <v>5</v>
@@ -1195,22 +1128,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2020-07-26</t>
-        </is>
-      </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2017-08-25</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2020-07-26</t>
-        </is>
-      </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2017-08-25</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1237,19 +1160,14 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>89119064</v>
+        <v>89119052</v>
       </c>
       <c r="B7" t="n">
-        <v>77506</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E7" t="n">
@@ -1277,10 +1195,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>532986.8860695376</v>
+        <v>532896</v>
       </c>
       <c r="R7" t="n">
-        <v>6910239.897575793</v>
+        <v>6910341</v>
       </c>
       <c r="S7" t="n">
         <v>5</v>
@@ -1310,19 +1228,9 @@
           <t>2020-07-26</t>
         </is>
       </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA7" t="inlineStr">
         <is>
           <t>2020-07-26</t>
-        </is>
-      </c>
-      <c r="AB7" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1349,37 +1257,32 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>89119053</v>
+        <v>89119061</v>
       </c>
       <c r="B8" t="n">
-        <v>77258</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1389,10 +1292,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>532877.1475416152</v>
+        <v>532905</v>
       </c>
       <c r="R8" t="n">
-        <v>6910321.104006157</v>
+        <v>6910240</v>
       </c>
       <c r="S8" t="n">
         <v>5</v>
@@ -1422,19 +1325,9 @@
           <t>2020-07-26</t>
         </is>
       </c>
-      <c r="Z8" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA8" t="inlineStr">
         <is>
           <t>2020-07-26</t>
-        </is>
-      </c>
-      <c r="AB8" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1461,37 +1354,32 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>89119063</v>
+        <v>89119064</v>
       </c>
       <c r="B9" t="n">
-        <v>78569</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1501,10 +1389,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>532974.9197036936</v>
+        <v>532987</v>
       </c>
       <c r="R9" t="n">
-        <v>6910225.833161629</v>
+        <v>6910240</v>
       </c>
       <c r="S9" t="n">
         <v>5</v>
@@ -1534,19 +1422,9 @@
           <t>2020-07-26</t>
         </is>
       </c>
-      <c r="Z9" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA9" t="inlineStr">
         <is>
           <t>2020-07-26</t>
-        </is>
-      </c>
-      <c r="AB9" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1573,67 +1451,48 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>89119054</v>
+        <v>121146985</v>
       </c>
       <c r="B10" t="n">
-        <v>56395</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Godkänd baserat på observatörens uppgifter</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="K10" t="inlineStr">
-        <is>
-          <t>pulli</t>
-        </is>
-      </c>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>pulli/nyligen flygga ungar</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>VSV Nymyran, Hls</t>
+          <t>Nymyran, Hls</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>532842.9230201059</v>
+        <v>532890</v>
       </c>
       <c r="R10" t="n">
-        <v>6910297.98948987</v>
+        <v>6910366</v>
       </c>
       <c r="S10" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1657,22 +1516,17 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2020-07-26</t>
-        </is>
-      </c>
-      <c r="Z10" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2024-11-04</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2020-07-26</t>
-        </is>
-      </c>
-      <c r="AB10" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2024-11-04</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>Garnlav På Tall</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1681,33 +1535,29 @@
       <c r="AE10" t="b">
         <v>0</v>
       </c>
+      <c r="AF10" t="inlineStr"/>
       <c r="AG10" t="b">
         <v>0</v>
       </c>
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Jan Henriksson</t>
+          <t>Annica Berglind</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Jan Henriksson</t>
+          <t>Annica Berglind</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>121146983</v>
+        <v>67288992</v>
       </c>
       <c r="B11" t="n">
-        <v>78343</v>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79084</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1733,19 +1583,21 @@
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
+      <c r="J11" t="inlineStr"/>
+      <c r="K11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Nymyran, Hls</t>
+          <t>Barrskog Ö Nymyran, Hls</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>532981</v>
+        <v>532475</v>
       </c>
       <c r="R11" t="n">
-        <v>6910252</v>
+        <v>6910556</v>
       </c>
       <c r="S11" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1769,12 +1621,12 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2024-11-04</t>
+          <t>2017-08-25</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>2024-11-04</t>
+          <t>2017-08-25</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1789,27 +1641,22 @@
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Annica Berglind</t>
+          <t>Jan Henriksson</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Annica Berglind</t>
+          <t>Jan Henriksson</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>121146969</v>
+        <v>89119053</v>
       </c>
       <c r="B12" t="n">
-        <v>95645</v>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79084</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1817,37 +1664,37 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>53</v>
+        <v>6446</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Nymyran, Hls</t>
+          <t>VSV Nymyran, Hls</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>532986</v>
+        <v>532877</v>
       </c>
       <c r="R12" t="n">
-        <v>6910219</v>
+        <v>6910321</v>
       </c>
       <c r="S12" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1871,12 +1718,12 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2024-11-04</t>
+          <t>2020-07-26</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>2024-11-04</t>
+          <t>2020-07-26</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1891,27 +1738,22 @@
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Annica Berglind</t>
+          <t>Jan Henriksson</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Annica Berglind</t>
+          <t>Jan Henriksson</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>121146976</v>
+        <v>121146973</v>
       </c>
       <c r="B13" t="n">
-        <v>78343</v>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79084</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1943,10 +1785,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>532590</v>
+        <v>532505</v>
       </c>
       <c r="R13" t="n">
-        <v>6910455</v>
+        <v>6910533</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2005,15 +1847,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>121146980</v>
+        <v>121146974</v>
       </c>
       <c r="B14" t="n">
-        <v>78343</v>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79084</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2045,10 +1882,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>532775</v>
+        <v>532543</v>
       </c>
       <c r="R14" t="n">
-        <v>6910332</v>
+        <v>6910505</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2107,15 +1944,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>121146979</v>
+        <v>121146976</v>
       </c>
       <c r="B15" t="n">
-        <v>78343</v>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79084</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2147,10 +1979,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>532733</v>
+        <v>532590</v>
       </c>
       <c r="R15" t="n">
-        <v>6910348</v>
+        <v>6910455</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2209,15 +2041,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>121146972</v>
+        <v>121146977</v>
       </c>
       <c r="B16" t="n">
-        <v>80564</v>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79084</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2225,21 +2052,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>1049</v>
+        <v>6446</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Kortskaftad ärgspik</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Microcalicium ahlneri</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2249,10 +2076,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>532667</v>
+        <v>532650</v>
       </c>
       <c r="R16" t="n">
-        <v>6910387</v>
+        <v>6910410</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2311,15 +2138,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>121146973</v>
+        <v>121146978</v>
       </c>
       <c r="B17" t="n">
-        <v>78343</v>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79084</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2351,10 +2173,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>532505</v>
+        <v>532668</v>
       </c>
       <c r="R17" t="n">
-        <v>6910533</v>
+        <v>6910385</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2413,37 +2235,32 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>121146984</v>
+        <v>121146979</v>
       </c>
       <c r="B18" t="n">
-        <v>90867</v>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79084</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>1503</v>
+        <v>6446</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Gräddporing</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Sidera lenis</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(P.Karst.) Miettinen</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2453,10 +2270,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>532952</v>
+        <v>532733</v>
       </c>
       <c r="R18" t="n">
-        <v>6910283</v>
+        <v>6910348</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2515,37 +2332,32 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>121146970</v>
+        <v>121146980</v>
       </c>
       <c r="B19" t="n">
-        <v>79592</v>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79084</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6456</v>
+        <v>6446</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2555,10 +2367,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>532591</v>
+        <v>532775</v>
       </c>
       <c r="R19" t="n">
-        <v>6910435</v>
+        <v>6910332</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2617,15 +2429,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>121146985</v>
+        <v>121146981</v>
       </c>
       <c r="B20" t="n">
-        <v>78607</v>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79084</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2633,21 +2440,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2657,10 +2464,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>532890</v>
+        <v>532844</v>
       </c>
       <c r="R20" t="n">
-        <v>6910366</v>
+        <v>6910318</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2695,18 +2502,12 @@
           <t>2024-11-04</t>
         </is>
       </c>
-      <c r="AC20" t="inlineStr">
-        <is>
-          <t>Garnlav På Tall</t>
-        </is>
-      </c>
       <c r="AD20" t="b">
         <v>0</v>
       </c>
       <c r="AE20" t="b">
         <v>0</v>
       </c>
-      <c r="AF20" t="inlineStr"/>
       <c r="AG20" t="b">
         <v>0</v>
       </c>
@@ -2728,12 +2529,7 @@
         <v>121146982</v>
       </c>
       <c r="B21" t="n">
-        <v>78343</v>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79084</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2827,15 +2623,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>121146981</v>
+        <v>121146983</v>
       </c>
       <c r="B22" t="n">
-        <v>78343</v>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79084</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2867,10 +2658,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>532844</v>
+        <v>532981</v>
       </c>
       <c r="R22" t="n">
-        <v>6910318</v>
+        <v>6910252</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2929,37 +2720,32 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>121146977</v>
+        <v>121146970</v>
       </c>
       <c r="B23" t="n">
-        <v>78343</v>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80336</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6446</v>
+        <v>6456</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2969,10 +2755,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>532650</v>
+        <v>532591</v>
       </c>
       <c r="R23" t="n">
-        <v>6910410</v>
+        <v>6910435</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3031,15 +2817,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>121146971</v>
+        <v>89119058</v>
       </c>
       <c r="B24" t="n">
-        <v>78344</v>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3047,37 +2828,37 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>228912</v>
+        <v>6458</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Nymyran, Hls</t>
+          <t>VSV Nymyran, Hls</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>532980</v>
+        <v>532875</v>
       </c>
       <c r="R24" t="n">
-        <v>6910252</v>
+        <v>6910261</v>
       </c>
       <c r="S24" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -3101,12 +2882,12 @@
       </c>
       <c r="Y24" t="inlineStr">
         <is>
-          <t>2024-11-04</t>
+          <t>2020-07-26</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
         <is>
-          <t>2024-11-04</t>
+          <t>2020-07-26</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3121,27 +2902,22 @@
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>Annica Berglind</t>
+          <t>Jan Henriksson</t>
         </is>
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>Annica Berglind</t>
+          <t>Jan Henriksson</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>121146978</v>
+        <v>89119063</v>
       </c>
       <c r="B25" t="n">
-        <v>78343</v>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3149,37 +2925,37 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6446</v>
+        <v>6458</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
-          <t>Nymyran, Hls</t>
+          <t>VSV Nymyran, Hls</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>532668</v>
+        <v>532975</v>
       </c>
       <c r="R25" t="n">
-        <v>6910385</v>
+        <v>6910226</v>
       </c>
       <c r="S25" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -3203,12 +2979,12 @@
       </c>
       <c r="Y25" t="inlineStr">
         <is>
-          <t>2024-11-04</t>
+          <t>2020-07-26</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
         <is>
-          <t>2024-11-04</t>
+          <t>2020-07-26</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3223,27 +2999,22 @@
       <c r="AT25" t="inlineStr"/>
       <c r="AW25" t="inlineStr">
         <is>
-          <t>Annica Berglind</t>
+          <t>Jan Henriksson</t>
         </is>
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>Annica Berglind</t>
+          <t>Jan Henriksson</t>
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>121146974</v>
+        <v>89119054</v>
       </c>
       <c r="B26" t="n">
-        <v>78343</v>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3251,37 +3022,51 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6446</v>
+        <v>100109</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
-        </is>
-      </c>
-      <c r="I26" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K26" t="inlineStr">
+        <is>
+          <t>pulli</t>
+        </is>
+      </c>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>pulli/nyligen flygga ungar</t>
+        </is>
+      </c>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Nymyran, Hls</t>
+          <t>VSV Nymyran, Hls</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>532543</v>
+        <v>532843</v>
       </c>
       <c r="R26" t="n">
-        <v>6910505</v>
+        <v>6910298</v>
       </c>
       <c r="S26" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -3305,12 +3090,12 @@
       </c>
       <c r="Y26" t="inlineStr">
         <is>
-          <t>2024-11-04</t>
+          <t>2020-07-26</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
         <is>
-          <t>2024-11-04</t>
+          <t>2020-07-26</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3325,15 +3110,417 @@
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
         <is>
+          <t>Jan Henriksson</t>
+        </is>
+      </c>
+      <c r="AX26" t="inlineStr">
+        <is>
+          <t>Jan Henriksson</t>
+        </is>
+      </c>
+      <c r="AY26" t="inlineStr"/>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>89119056</v>
+      </c>
+      <c r="B27" t="n">
+        <v>57141</v>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E27" t="n">
+        <v>100138</v>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>Tjäder</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>Tetrao urogallus</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K27" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L27" t="inlineStr">
+        <is>
+          <t>hona</t>
+        </is>
+      </c>
+      <c r="P27" t="inlineStr">
+        <is>
+          <t>VSV Nymyran, Hls</t>
+        </is>
+      </c>
+      <c r="Q27" t="n">
+        <v>532857</v>
+      </c>
+      <c r="R27" t="n">
+        <v>6910268</v>
+      </c>
+      <c r="S27" t="n">
+        <v>5</v>
+      </c>
+      <c r="T27" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U27" t="inlineStr">
+        <is>
+          <t>Ljusdal</t>
+        </is>
+      </c>
+      <c r="V27" t="inlineStr">
+        <is>
+          <t>Hälsingland</t>
+        </is>
+      </c>
+      <c r="W27" t="inlineStr">
+        <is>
+          <t>Ramsjö</t>
+        </is>
+      </c>
+      <c r="Y27" t="inlineStr">
+        <is>
+          <t>2020-07-26</t>
+        </is>
+      </c>
+      <c r="AA27" t="inlineStr">
+        <is>
+          <t>2020-07-26</t>
+        </is>
+      </c>
+      <c r="AD27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT27" t="inlineStr"/>
+      <c r="AW27" t="inlineStr">
+        <is>
+          <t>Jan Henriksson</t>
+        </is>
+      </c>
+      <c r="AX27" t="inlineStr">
+        <is>
+          <t>Jan Henriksson</t>
+        </is>
+      </c>
+      <c r="AY27" t="inlineStr"/>
+    </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>67288989</v>
+      </c>
+      <c r="B28" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E28" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr"/>
+      <c r="P28" t="inlineStr">
+        <is>
+          <t>Barrskog Ö Nymyrdalen, Hls</t>
+        </is>
+      </c>
+      <c r="Q28" t="n">
+        <v>532455</v>
+      </c>
+      <c r="R28" t="n">
+        <v>6910565</v>
+      </c>
+      <c r="S28" t="n">
+        <v>5</v>
+      </c>
+      <c r="T28" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U28" t="inlineStr">
+        <is>
+          <t>Ljusdal</t>
+        </is>
+      </c>
+      <c r="V28" t="inlineStr">
+        <is>
+          <t>Hälsingland</t>
+        </is>
+      </c>
+      <c r="W28" t="inlineStr">
+        <is>
+          <t>Ramsjö</t>
+        </is>
+      </c>
+      <c r="Y28" t="inlineStr">
+        <is>
+          <t>2017-08-25</t>
+        </is>
+      </c>
+      <c r="AA28" t="inlineStr">
+        <is>
+          <t>2017-08-25</t>
+        </is>
+      </c>
+      <c r="AD28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT28" t="inlineStr"/>
+      <c r="AW28" t="inlineStr">
+        <is>
+          <t>Jan Henriksson</t>
+        </is>
+      </c>
+      <c r="AX28" t="inlineStr">
+        <is>
+          <t>Jan Henriksson</t>
+        </is>
+      </c>
+      <c r="AY28" t="inlineStr"/>
+    </row>
+    <row r="29">
+      <c r="A29" t="n">
+        <v>67288990</v>
+      </c>
+      <c r="B29" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E29" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr"/>
+      <c r="P29" t="inlineStr">
+        <is>
+          <t>Barrskog Ö Nymyrdalen, Hls</t>
+        </is>
+      </c>
+      <c r="Q29" t="n">
+        <v>532504</v>
+      </c>
+      <c r="R29" t="n">
+        <v>6910604</v>
+      </c>
+      <c r="S29" t="n">
+        <v>5</v>
+      </c>
+      <c r="T29" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U29" t="inlineStr">
+        <is>
+          <t>Ljusdal</t>
+        </is>
+      </c>
+      <c r="V29" t="inlineStr">
+        <is>
+          <t>Hälsingland</t>
+        </is>
+      </c>
+      <c r="W29" t="inlineStr">
+        <is>
+          <t>Ramsjö</t>
+        </is>
+      </c>
+      <c r="Y29" t="inlineStr">
+        <is>
+          <t>2017-08-25</t>
+        </is>
+      </c>
+      <c r="AA29" t="inlineStr">
+        <is>
+          <t>2017-08-25</t>
+        </is>
+      </c>
+      <c r="AD29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT29" t="inlineStr"/>
+      <c r="AW29" t="inlineStr">
+        <is>
+          <t>Jan Henriksson</t>
+        </is>
+      </c>
+      <c r="AX29" t="inlineStr">
+        <is>
+          <t>Jan Henriksson</t>
+        </is>
+      </c>
+      <c r="AY29" t="inlineStr"/>
+    </row>
+    <row r="30">
+      <c r="A30" t="n">
+        <v>121146971</v>
+      </c>
+      <c r="B30" t="n">
+        <v>79085</v>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E30" t="n">
+        <v>228912</v>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>Mörk kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>Carbonicola myrmecina</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr"/>
+      <c r="P30" t="inlineStr">
+        <is>
+          <t>Nymyran, Hls</t>
+        </is>
+      </c>
+      <c r="Q30" t="n">
+        <v>532980</v>
+      </c>
+      <c r="R30" t="n">
+        <v>6910252</v>
+      </c>
+      <c r="S30" t="n">
+        <v>10</v>
+      </c>
+      <c r="T30" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U30" t="inlineStr">
+        <is>
+          <t>Ljusdal</t>
+        </is>
+      </c>
+      <c r="V30" t="inlineStr">
+        <is>
+          <t>Hälsingland</t>
+        </is>
+      </c>
+      <c r="W30" t="inlineStr">
+        <is>
+          <t>Ramsjö</t>
+        </is>
+      </c>
+      <c r="Y30" t="inlineStr">
+        <is>
+          <t>2024-11-04</t>
+        </is>
+      </c>
+      <c r="AA30" t="inlineStr">
+        <is>
+          <t>2024-11-04</t>
+        </is>
+      </c>
+      <c r="AD30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT30" t="inlineStr"/>
+      <c r="AW30" t="inlineStr">
+        <is>
           <t>Annica Berglind</t>
         </is>
       </c>
-      <c r="AX26" t="inlineStr">
+      <c r="AX30" t="inlineStr">
         <is>
           <t>Annica Berglind</t>
         </is>
       </c>
-      <c r="AY26" t="inlineStr"/>
+      <c r="AY30" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 31463-2022 artfynd.xlsx
+++ b/artfynd/A 31463-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY30"/>
+  <dimension ref="A1:AZ30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -769,6 +774,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121146969</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -866,6 +876,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121146972</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -963,6 +978,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121146984</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1060,6 +1080,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/89119066</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1157,6 +1182,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/67288988</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1254,6 +1284,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/89119052</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1351,6 +1386,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/89119061</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1448,6 +1488,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/89119064</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1551,6 +1596,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121146985</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1650,6 +1700,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/67288992</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1747,6 +1802,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/89119053</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1844,6 +1904,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121146973</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -1941,6 +2006,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121146974</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2038,6 +2108,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121146976</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2135,6 +2210,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121146977</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2232,6 +2312,11 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121146978</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2329,6 +2414,11 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121146979</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2426,6 +2516,11 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121146980</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2523,6 +2618,11 @@
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121146981</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -2620,6 +2720,11 @@
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121146982</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -2717,6 +2822,11 @@
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121146983</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -2814,6 +2924,11 @@
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121146970</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -2911,6 +3026,11 @@
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/89119058</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -3008,6 +3128,11 @@
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/89119063</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -3119,6 +3244,11 @@
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/89119054</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -3230,6 +3360,11 @@
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
+      <c r="AZ27" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/89119056</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -3327,6 +3462,11 @@
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
+      <c r="AZ28" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/67288989</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -3424,6 +3564,11 @@
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
+      <c r="AZ29" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/67288990</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -3521,8 +3666,44 @@
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
+      <c r="AZ30" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121146971</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ28" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ29" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ30" r:id="rId29"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>